--- a/documents/2026/DtmtExport -2026-05-18_135022.xlsx
+++ b/documents/2026/DtmtExport -2026-05-18_135022.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pertturantanen/Rprojects/FIN-FDI-data-call/documents/2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://lukefinland-my.sharepoint.com/personal/joanne_demmler_luke_fi/Documents/Projects/FIN-FDI-data-call/documents/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4961BBA0-F5E2-3D4C-8B48-79FF744BA3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{4961BBA0-F5E2-3D4C-8B48-79FF744BA3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12F3A5DC-3380-43C9-A0DD-8C4C0787C185}"/>
   <bookViews>
-    <workbookView xWindow="4500" yWindow="600" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28845" yWindow="240" windowWidth="27375" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
@@ -422,13 +422,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -441,9 +434,17 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -501,9 +502,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -520,7 +518,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -856,33 +859,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.6640625" customWidth="1"/>
     <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="26" style="9" customWidth="1"/>
-    <col min="10" max="10" width="33.5" customWidth="1"/>
-    <col min="11" max="11" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" style="8" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26" style="8" customWidth="1"/>
+    <col min="10" max="10" width="33.44140625" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="67.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="27.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="59.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="59.44140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="67.33203125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="66.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="66.44140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="20.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>65</v>
       </c>
@@ -898,7 +901,7 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -907,7 +910,7 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -953,36 +956,36 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="11"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="10"/>
       <c r="J2" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="10"/>
-      <c r="T2" s="10"/>
-      <c r="U2" s="10"/>
-      <c r="V2" s="10"/>
-      <c r="W2" s="10"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
     </row>
-    <row r="3" spans="1:23" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -998,7 +1001,7 @@
       <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="G3" t="s">
@@ -1007,10 +1010,10 @@
       <c r="H3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="11" t="s">
         <v>27</v>
       </c>
       <c r="K3" t="s">
@@ -1044,7 +1047,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1060,7 +1063,7 @@
       <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="G4" t="s">
@@ -1069,10 +1072,10 @@
       <c r="H4" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="11" t="s">
         <v>38</v>
       </c>
       <c r="K4" t="s">
@@ -1106,7 +1109,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="64" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1122,7 +1125,7 @@
       <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>24</v>
       </c>
       <c r="G5" t="s">
@@ -1131,10 +1134,10 @@
       <c r="H5" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="11" t="s">
         <v>40</v>
       </c>
       <c r="K5" t="s">
@@ -1168,58 +1171,58 @@
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="48" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="11" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="11" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="11" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:23" s="3" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" s="3" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>5333</v>
       </c>
@@ -1232,7 +1235,7 @@
       <c r="E9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1241,10 +1244,10 @@
       <c r="H9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5" t="s">
         <v>46</v>
       </c>
       <c r="K9" s="3" t="s">
@@ -1281,7 +1284,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:23" s="2" customFormat="1" ht="48" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>5248</v>
       </c>
@@ -1294,7 +1297,7 @@
       <c r="E10" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G10" s="2" t="s">
@@ -1303,10 +1306,10 @@
       <c r="H10" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="7" t="s">
+      <c r="J10" s="6" t="s">
         <v>51</v>
       </c>
       <c r="K10" s="2" t="s">
@@ -1349,7 +1352,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:23" s="2" customFormat="1" ht="64" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" s="2" customFormat="1" ht="72" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>5247</v>
       </c>
@@ -1362,7 +1365,7 @@
       <c r="E11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -1371,10 +1374,10 @@
       <c r="H11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="6" t="s">
         <v>59</v>
       </c>
       <c r="K11" s="2" t="s">
